--- a/artfynd/A 11754-2024 artfynd.xlsx
+++ b/artfynd/A 11754-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122132182</v>
+        <v>122132185</v>
       </c>
       <c r="B2" t="n">
-        <v>57365</v>
+        <v>57385</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,16 +691,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>568987</v>
+        <v>568955</v>
       </c>
       <c r="R2" t="n">
-        <v>7107945</v>
+        <v>7108055</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,11 +751,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-10-08</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>hackspår äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122131771</v>
+        <v>122131750</v>
       </c>
       <c r="B3" t="n">
-        <v>79741</v>
+        <v>78639</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>569099</v>
+        <v>568985</v>
       </c>
       <c r="R3" t="n">
-        <v>7107950</v>
+        <v>7107948</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122131763</v>
+        <v>122132203</v>
       </c>
       <c r="B4" t="n">
-        <v>78632</v>
+        <v>57385</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>568969</v>
+        <v>569020</v>
       </c>
       <c r="R4" t="n">
-        <v>7107966</v>
+        <v>7107958</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -986,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122132203</v>
+        <v>122131763</v>
       </c>
       <c r="B5" t="n">
-        <v>57381</v>
+        <v>78639</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1002,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1026,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>569020</v>
+        <v>568969</v>
       </c>
       <c r="R5" t="n">
-        <v>7107958</v>
+        <v>7107966</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1091,7 +1086,7 @@
         <v>122132183</v>
       </c>
       <c r="B6" t="n">
-        <v>57365</v>
+        <v>57369</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1195,10 +1190,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122131824</v>
+        <v>122131801</v>
       </c>
       <c r="B7" t="n">
-        <v>79741</v>
+        <v>90754</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1207,25 +1202,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6461</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1235,10 +1230,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>569109</v>
+        <v>569094</v>
       </c>
       <c r="R7" t="n">
-        <v>7107936</v>
+        <v>7107950</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1297,10 +1292,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122132185</v>
+        <v>122131824</v>
       </c>
       <c r="B8" t="n">
-        <v>57381</v>
+        <v>79748</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1309,25 +1304,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>6461</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1337,10 +1332,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>568955</v>
+        <v>569109</v>
       </c>
       <c r="R8" t="n">
-        <v>7108055</v>
+        <v>7107936</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1399,10 +1394,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122131750</v>
+        <v>122132182</v>
       </c>
       <c r="B9" t="n">
-        <v>78632</v>
+        <v>57369</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1415,21 +1410,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1439,10 +1434,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>568985</v>
+        <v>568987</v>
       </c>
       <c r="R9" t="n">
-        <v>7107948</v>
+        <v>7107945</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1475,6 +1470,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-10-08</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>hackspår äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1501,10 +1501,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122131801</v>
+        <v>122131771</v>
       </c>
       <c r="B10" t="n">
-        <v>90745</v>
+        <v>79748</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1513,25 +1513,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>6461</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1541,7 +1541,7 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>569094</v>
+        <v>569099</v>
       </c>
       <c r="R10" t="n">
         <v>7107950</v>

--- a/artfynd/A 11754-2024 artfynd.xlsx
+++ b/artfynd/A 11754-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122131801</v>
+        <v>122132183</v>
       </c>
       <c r="B2" t="n">
-        <v>90779</v>
+        <v>57374</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>569094</v>
+        <v>569079</v>
       </c>
       <c r="R2" t="n">
-        <v>7107950</v>
+        <v>7107955</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,6 +751,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-10-08</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>äldre hackspår</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122131771</v>
+        <v>122131763</v>
       </c>
       <c r="B3" t="n">
-        <v>79754</v>
+        <v>78645</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +794,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>569099</v>
+        <v>568969</v>
       </c>
       <c r="R3" t="n">
-        <v>7107950</v>
+        <v>7107966</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122132182</v>
+        <v>122132203</v>
       </c>
       <c r="B4" t="n">
-        <v>57374</v>
+        <v>57390</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,16 +900,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -919,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>568987</v>
+        <v>569020</v>
       </c>
       <c r="R4" t="n">
-        <v>7107945</v>
+        <v>7107958</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -955,11 +960,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-10-08</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>hackspår äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -986,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122132203</v>
+        <v>122131750</v>
       </c>
       <c r="B5" t="n">
-        <v>57390</v>
+        <v>78645</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1002,21 +1002,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1026,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>569020</v>
+        <v>568985</v>
       </c>
       <c r="R5" t="n">
-        <v>7107958</v>
+        <v>7107948</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1088,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122131824</v>
+        <v>122131801</v>
       </c>
       <c r="B6" t="n">
-        <v>79754</v>
+        <v>90779</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1100,25 +1100,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6461</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1128,10 +1128,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>569109</v>
+        <v>569094</v>
       </c>
       <c r="R6" t="n">
-        <v>7107936</v>
+        <v>7107950</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1190,10 +1190,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122131763</v>
+        <v>122131771</v>
       </c>
       <c r="B7" t="n">
-        <v>78645</v>
+        <v>79754</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1202,25 +1202,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1230,10 +1230,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>568969</v>
+        <v>569099</v>
       </c>
       <c r="R7" t="n">
-        <v>7107966</v>
+        <v>7107950</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1292,10 +1292,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122132183</v>
+        <v>122131824</v>
       </c>
       <c r="B8" t="n">
-        <v>57374</v>
+        <v>79754</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1304,25 +1304,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6461</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1332,10 +1332,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>569079</v>
+        <v>569109</v>
       </c>
       <c r="R8" t="n">
-        <v>7107955</v>
+        <v>7107936</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1368,11 +1368,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-10-08</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>äldre hackspår</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1399,10 +1394,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122131750</v>
+        <v>122132182</v>
       </c>
       <c r="B9" t="n">
-        <v>78645</v>
+        <v>57374</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1415,21 +1410,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1439,10 +1434,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>568985</v>
+        <v>568987</v>
       </c>
       <c r="R9" t="n">
-        <v>7107948</v>
+        <v>7107945</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1475,6 +1470,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-10-08</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>hackspår äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 11754-2024 artfynd.xlsx
+++ b/artfynd/A 11754-2024 artfynd.xlsx
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122131763</v>
+        <v>122131750</v>
       </c>
       <c r="B3" t="n">
-        <v>78645</v>
+        <v>78646</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>568969</v>
+        <v>568985</v>
       </c>
       <c r="R3" t="n">
-        <v>7107966</v>
+        <v>7107948</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -986,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122131750</v>
+        <v>122131824</v>
       </c>
       <c r="B5" t="n">
-        <v>78645</v>
+        <v>79755</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -998,25 +998,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1026,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>568985</v>
+        <v>569109</v>
       </c>
       <c r="R5" t="n">
-        <v>7107948</v>
+        <v>7107936</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1088,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122131801</v>
+        <v>122132182</v>
       </c>
       <c r="B6" t="n">
-        <v>90779</v>
+        <v>57374</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1104,21 +1104,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1128,10 +1128,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>569094</v>
+        <v>568987</v>
       </c>
       <c r="R6" t="n">
-        <v>7107950</v>
+        <v>7107945</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1164,6 +1164,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-10-08</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>hackspår äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1190,10 +1195,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122131771</v>
+        <v>122132185</v>
       </c>
       <c r="B7" t="n">
-        <v>79754</v>
+        <v>57390</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1202,25 +1207,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6461</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1230,10 +1235,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>569099</v>
+        <v>568955</v>
       </c>
       <c r="R7" t="n">
-        <v>7107950</v>
+        <v>7108055</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1292,10 +1297,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122131824</v>
+        <v>122131801</v>
       </c>
       <c r="B8" t="n">
-        <v>79754</v>
+        <v>90789</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1304,25 +1309,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6461</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1332,10 +1337,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>569109</v>
+        <v>569094</v>
       </c>
       <c r="R8" t="n">
-        <v>7107936</v>
+        <v>7107950</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1394,10 +1399,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122132182</v>
+        <v>122131771</v>
       </c>
       <c r="B9" t="n">
-        <v>57374</v>
+        <v>79755</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1406,25 +1411,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6461</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1434,10 +1439,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>568987</v>
+        <v>569099</v>
       </c>
       <c r="R9" t="n">
-        <v>7107945</v>
+        <v>7107950</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1470,11 +1475,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-10-08</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>hackspår äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1501,10 +1501,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122132185</v>
+        <v>122131763</v>
       </c>
       <c r="B10" t="n">
-        <v>57390</v>
+        <v>78646</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1517,21 +1517,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1541,10 +1541,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>568955</v>
+        <v>568969</v>
       </c>
       <c r="R10" t="n">
-        <v>7108055</v>
+        <v>7107966</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>

--- a/artfynd/A 11754-2024 artfynd.xlsx
+++ b/artfynd/A 11754-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122132183</v>
+        <v>122132182</v>
       </c>
       <c r="B2" t="n">
         <v>57374</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>569079</v>
+        <v>568987</v>
       </c>
       <c r="R2" t="n">
-        <v>7107955</v>
+        <v>7107945</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>äldre hackspår</t>
+          <t>hackspår äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122131750</v>
+        <v>122132183</v>
       </c>
       <c r="B3" t="n">
-        <v>78646</v>
+        <v>57374</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>568985</v>
+        <v>569079</v>
       </c>
       <c r="R3" t="n">
-        <v>7107948</v>
+        <v>7107955</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -858,6 +858,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-10-08</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>äldre hackspår</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122132203</v>
+        <v>122131801</v>
       </c>
       <c r="B4" t="n">
-        <v>57390</v>
+        <v>90789</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,21 +905,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>569020</v>
+        <v>569094</v>
       </c>
       <c r="R4" t="n">
-        <v>7107958</v>
+        <v>7107950</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -986,10 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122131824</v>
+        <v>122131750</v>
       </c>
       <c r="B5" t="n">
-        <v>79755</v>
+        <v>78646</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -998,25 +1003,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1026,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>569109</v>
+        <v>568985</v>
       </c>
       <c r="R5" t="n">
-        <v>7107936</v>
+        <v>7107948</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1088,10 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122132182</v>
+        <v>122131771</v>
       </c>
       <c r="B6" t="n">
-        <v>57374</v>
+        <v>79755</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1100,25 +1105,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6461</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1128,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>568987</v>
+        <v>569099</v>
       </c>
       <c r="R6" t="n">
-        <v>7107945</v>
+        <v>7107950</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1164,11 +1169,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-10-08</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>hackspår äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1297,10 +1297,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122131801</v>
+        <v>122131763</v>
       </c>
       <c r="B8" t="n">
-        <v>90789</v>
+        <v>78646</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1313,21 +1313,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1337,10 +1337,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>569094</v>
+        <v>568969</v>
       </c>
       <c r="R8" t="n">
-        <v>7107950</v>
+        <v>7107966</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1399,7 +1399,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122131771</v>
+        <v>122131824</v>
       </c>
       <c r="B9" t="n">
         <v>79755</v>
@@ -1439,10 +1439,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>569099</v>
+        <v>569109</v>
       </c>
       <c r="R9" t="n">
-        <v>7107950</v>
+        <v>7107936</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1501,10 +1501,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122131763</v>
+        <v>122132203</v>
       </c>
       <c r="B10" t="n">
-        <v>78646</v>
+        <v>57390</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1517,21 +1517,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1541,10 +1541,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>568969</v>
+        <v>569020</v>
       </c>
       <c r="R10" t="n">
-        <v>7107966</v>
+        <v>7107958</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>

--- a/artfynd/A 11754-2024 artfynd.xlsx
+++ b/artfynd/A 11754-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122132182</v>
       </c>
       <c r="B2" t="n">
-        <v>57374</v>
+        <v>57379</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122132183</v>
+        <v>122132203</v>
       </c>
       <c r="B3" t="n">
-        <v>57374</v>
+        <v>57395</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,16 +798,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>569079</v>
+        <v>569020</v>
       </c>
       <c r="R3" t="n">
-        <v>7107955</v>
+        <v>7107958</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -858,11 +858,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-10-08</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>äldre hackspår</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -892,7 +887,7 @@
         <v>122131801</v>
       </c>
       <c r="B4" t="n">
-        <v>90789</v>
+        <v>90801</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -991,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122131750</v>
+        <v>122131763</v>
       </c>
       <c r="B5" t="n">
-        <v>78646</v>
+        <v>78651</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1031,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>568985</v>
+        <v>568969</v>
       </c>
       <c r="R5" t="n">
-        <v>7107948</v>
+        <v>7107966</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1096,7 +1091,7 @@
         <v>122131771</v>
       </c>
       <c r="B6" t="n">
-        <v>79755</v>
+        <v>79760</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1195,10 +1190,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122132185</v>
+        <v>122132183</v>
       </c>
       <c r="B7" t="n">
-        <v>57390</v>
+        <v>57379</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1211,16 +1206,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1235,10 +1230,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>568955</v>
+        <v>569079</v>
       </c>
       <c r="R7" t="n">
-        <v>7108055</v>
+        <v>7107955</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1271,6 +1266,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-10-08</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>äldre hackspår</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1297,10 +1297,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122131763</v>
+        <v>122131824</v>
       </c>
       <c r="B8" t="n">
-        <v>78646</v>
+        <v>79760</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1309,25 +1309,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1337,10 +1337,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>568969</v>
+        <v>569109</v>
       </c>
       <c r="R8" t="n">
-        <v>7107966</v>
+        <v>7107936</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1399,10 +1399,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122131824</v>
+        <v>122131750</v>
       </c>
       <c r="B9" t="n">
-        <v>79755</v>
+        <v>78651</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1411,25 +1411,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1439,10 +1439,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>569109</v>
+        <v>568985</v>
       </c>
       <c r="R9" t="n">
-        <v>7107936</v>
+        <v>7107948</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1501,10 +1501,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122132203</v>
+        <v>122132185</v>
       </c>
       <c r="B10" t="n">
-        <v>57390</v>
+        <v>57395</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1541,10 +1541,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>569020</v>
+        <v>568955</v>
       </c>
       <c r="R10" t="n">
-        <v>7107958</v>
+        <v>7108055</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>

--- a/artfynd/A 11754-2024 artfynd.xlsx
+++ b/artfynd/A 11754-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122132182</v>
+        <v>122131824</v>
       </c>
       <c r="B2" t="n">
-        <v>57379</v>
+        <v>79760</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6461</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>568987</v>
+        <v>569109</v>
       </c>
       <c r="R2" t="n">
-        <v>7107945</v>
+        <v>7107936</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,11 +751,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-10-08</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>hackspår äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122132203</v>
+        <v>122132183</v>
       </c>
       <c r="B3" t="n">
-        <v>57395</v>
+        <v>57379</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,16 +793,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -822,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>569020</v>
+        <v>569079</v>
       </c>
       <c r="R3" t="n">
-        <v>7107958</v>
+        <v>7107955</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -858,6 +853,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-10-08</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>äldre hackspår</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122131801</v>
+        <v>122132182</v>
       </c>
       <c r="B4" t="n">
-        <v>90801</v>
+        <v>57379</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>569094</v>
+        <v>568987</v>
       </c>
       <c r="R4" t="n">
-        <v>7107950</v>
+        <v>7107945</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -960,6 +960,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-10-08</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>hackspår äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1190,10 +1195,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122132183</v>
+        <v>122131750</v>
       </c>
       <c r="B7" t="n">
-        <v>57379</v>
+        <v>78651</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1206,21 +1211,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1230,10 +1235,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>569079</v>
+        <v>568985</v>
       </c>
       <c r="R7" t="n">
-        <v>7107955</v>
+        <v>7107948</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1266,11 +1271,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-10-08</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>äldre hackspår</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1297,10 +1297,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122131824</v>
+        <v>122132185</v>
       </c>
       <c r="B8" t="n">
-        <v>79760</v>
+        <v>57395</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1309,25 +1309,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6461</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1337,10 +1337,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>569109</v>
+        <v>568955</v>
       </c>
       <c r="R8" t="n">
-        <v>7107936</v>
+        <v>7108055</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1399,10 +1399,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122131750</v>
+        <v>122131801</v>
       </c>
       <c r="B9" t="n">
-        <v>78651</v>
+        <v>90808</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1415,21 +1415,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1439,10 +1439,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>568985</v>
+        <v>569094</v>
       </c>
       <c r="R9" t="n">
-        <v>7107948</v>
+        <v>7107950</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1501,7 +1501,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122132185</v>
+        <v>122132203</v>
       </c>
       <c r="B10" t="n">
         <v>57395</v>
@@ -1541,10 +1541,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>568955</v>
+        <v>569020</v>
       </c>
       <c r="R10" t="n">
-        <v>7108055</v>
+        <v>7107958</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>

--- a/artfynd/A 11754-2024 artfynd.xlsx
+++ b/artfynd/A 11754-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122131824</v>
+        <v>122132183</v>
       </c>
       <c r="B2" t="n">
-        <v>79760</v>
+        <v>57379</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,20 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6461</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Norrlandslav</t>
-        </is>
+        <v>100109</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>569109</v>
+        <v>569079</v>
       </c>
       <c r="R2" t="n">
-        <v>7107936</v>
+        <v>7107955</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,6 +746,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-10-08</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>äldre hackspår</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122132183</v>
+        <v>122131763</v>
       </c>
       <c r="B3" t="n">
-        <v>57379</v>
+        <v>78652</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
+        <v>6425</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>569079</v>
+        <v>568969</v>
       </c>
       <c r="R3" t="n">
-        <v>7107955</v>
+        <v>7107966</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -853,11 +848,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-10-08</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>äldre hackspår</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,10 +874,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122132182</v>
+        <v>122131801</v>
       </c>
       <c r="B4" t="n">
-        <v>57379</v>
+        <v>90813</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,21 +890,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
+        <v>1202</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>568987</v>
+        <v>569094</v>
       </c>
       <c r="R4" t="n">
-        <v>7107945</v>
+        <v>7107950</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -960,11 +945,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-10-08</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>hackspår äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -991,10 +971,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122131763</v>
+        <v>122131771</v>
       </c>
       <c r="B5" t="n">
-        <v>78651</v>
+        <v>79761</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1003,25 +983,20 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
+        <v>6461</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,10 +1006,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>568969</v>
+        <v>569099</v>
       </c>
       <c r="R5" t="n">
-        <v>7107966</v>
+        <v>7107950</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1093,10 +1068,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122131771</v>
+        <v>122131750</v>
       </c>
       <c r="B6" t="n">
-        <v>79760</v>
+        <v>78652</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1105,25 +1080,20 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6461</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Norrlandslav</t>
-        </is>
+        <v>6425</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1133,10 +1103,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>569099</v>
+        <v>568985</v>
       </c>
       <c r="R6" t="n">
-        <v>7107950</v>
+        <v>7107948</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1195,10 +1165,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122131750</v>
+        <v>122132182</v>
       </c>
       <c r="B7" t="n">
-        <v>78651</v>
+        <v>57379</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1211,21 +1181,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
+        <v>100109</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1235,10 +1200,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>568985</v>
+        <v>568987</v>
       </c>
       <c r="R7" t="n">
-        <v>7107948</v>
+        <v>7107945</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1271,6 +1236,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-10-08</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>hackspår äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1315,11 +1285,6 @@
       <c r="E8" t="n">
         <v>100049</v>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
-      </c>
       <c r="G8" t="inlineStr">
         <is>
           <t>Dryocopus martius</t>
@@ -1399,10 +1364,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122131801</v>
+        <v>122132203</v>
       </c>
       <c r="B9" t="n">
-        <v>90808</v>
+        <v>57395</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1415,21 +1380,16 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Ullticka</t>
-        </is>
+        <v>100049</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1439,10 +1399,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>569094</v>
+        <v>569020</v>
       </c>
       <c r="R9" t="n">
-        <v>7107950</v>
+        <v>7107958</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1501,10 +1461,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122132203</v>
+        <v>122131824</v>
       </c>
       <c r="B10" t="n">
-        <v>57395</v>
+        <v>79761</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1513,25 +1473,20 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
+        <v>6461</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1541,10 +1496,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>569020</v>
+        <v>569109</v>
       </c>
       <c r="R10" t="n">
-        <v>7107958</v>
+        <v>7107936</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>

--- a/artfynd/A 11754-2024 artfynd.xlsx
+++ b/artfynd/A 11754-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122132183</v>
       </c>
       <c r="B2" t="n">
-        <v>57379</v>
+        <v>57383</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -692,6 +692,11 @@
       </c>
       <c r="E2" t="n">
         <v>100109</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -780,7 +785,7 @@
         <v>122131763</v>
       </c>
       <c r="B3" t="n">
-        <v>78652</v>
+        <v>78656</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,6 +799,11 @@
       </c>
       <c r="E3" t="n">
         <v>6425</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -874,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122131801</v>
+        <v>122132182</v>
       </c>
       <c r="B4" t="n">
-        <v>90813</v>
+        <v>57383</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -890,16 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>100109</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -909,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>569094</v>
+        <v>568987</v>
       </c>
       <c r="R4" t="n">
-        <v>7107950</v>
+        <v>7107945</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -945,6 +960,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-10-08</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>hackspår äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -971,10 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122131771</v>
+        <v>122132185</v>
       </c>
       <c r="B5" t="n">
-        <v>79761</v>
+        <v>57399</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -983,20 +1003,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6461</v>
+        <v>100049</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1006,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>569099</v>
+        <v>568955</v>
       </c>
       <c r="R5" t="n">
-        <v>7107950</v>
+        <v>7108055</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1068,10 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122131750</v>
+        <v>122131824</v>
       </c>
       <c r="B6" t="n">
-        <v>78652</v>
+        <v>79765</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1080,20 +1105,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6461</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Norrlandslav</t>
+        </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1103,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>568985</v>
+        <v>569109</v>
       </c>
       <c r="R6" t="n">
-        <v>7107948</v>
+        <v>7107936</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1165,10 +1195,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122132182</v>
+        <v>122132203</v>
       </c>
       <c r="B7" t="n">
-        <v>57379</v>
+        <v>57399</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1181,11 +1211,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>100049</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1200,10 +1235,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>568987</v>
+        <v>569020</v>
       </c>
       <c r="R7" t="n">
-        <v>7107945</v>
+        <v>7107958</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1236,11 +1271,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-10-08</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>hackspår äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1267,10 +1297,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122132185</v>
+        <v>122131801</v>
       </c>
       <c r="B8" t="n">
-        <v>57395</v>
+        <v>90826</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1283,16 +1313,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>1202</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1302,10 +1337,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>568955</v>
+        <v>569094</v>
       </c>
       <c r="R8" t="n">
-        <v>7108055</v>
+        <v>7107950</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1364,10 +1399,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122132203</v>
+        <v>122131771</v>
       </c>
       <c r="B9" t="n">
-        <v>57395</v>
+        <v>79765</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1376,20 +1411,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>6461</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Norrlandslav</t>
+        </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1399,10 +1439,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>569020</v>
+        <v>569099</v>
       </c>
       <c r="R9" t="n">
-        <v>7107958</v>
+        <v>7107950</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1461,10 +1501,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122131824</v>
+        <v>122131750</v>
       </c>
       <c r="B10" t="n">
-        <v>79761</v>
+        <v>78656</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1473,20 +1513,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6461</v>
+        <v>6425</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1496,10 +1541,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>569109</v>
+        <v>568985</v>
       </c>
       <c r="R10" t="n">
-        <v>7107936</v>
+        <v>7107948</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>

--- a/artfynd/A 11754-2024 artfynd.xlsx
+++ b/artfynd/A 11754-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122132183</v>
+        <v>122131771</v>
       </c>
       <c r="B2" t="n">
-        <v>57383</v>
+        <v>79765</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6461</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>569079</v>
+        <v>569099</v>
       </c>
       <c r="R2" t="n">
-        <v>7107955</v>
+        <v>7107950</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,11 +751,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-10-08</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>äldre hackspår</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122131763</v>
+        <v>122131801</v>
       </c>
       <c r="B3" t="n">
-        <v>78656</v>
+        <v>90839</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>568969</v>
+        <v>569094</v>
       </c>
       <c r="R3" t="n">
-        <v>7107966</v>
+        <v>7107950</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122132182</v>
+        <v>122131824</v>
       </c>
       <c r="B4" t="n">
-        <v>57383</v>
+        <v>79765</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -896,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6461</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>568987</v>
+        <v>569109</v>
       </c>
       <c r="R4" t="n">
-        <v>7107945</v>
+        <v>7107936</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -960,11 +955,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-10-08</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>hackspår äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -991,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122132185</v>
+        <v>122132183</v>
       </c>
       <c r="B5" t="n">
-        <v>57399</v>
+        <v>57383</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1007,16 +997,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1031,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>568955</v>
+        <v>569079</v>
       </c>
       <c r="R5" t="n">
-        <v>7108055</v>
+        <v>7107955</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1067,6 +1057,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-10-08</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>äldre hackspår</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1093,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122131824</v>
+        <v>122132203</v>
       </c>
       <c r="B6" t="n">
-        <v>79765</v>
+        <v>57399</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1105,25 +1100,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6461</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1133,10 +1128,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>569109</v>
+        <v>569020</v>
       </c>
       <c r="R6" t="n">
-        <v>7107936</v>
+        <v>7107958</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1195,10 +1190,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122132203</v>
+        <v>122131763</v>
       </c>
       <c r="B7" t="n">
-        <v>57399</v>
+        <v>78656</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1211,21 +1206,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1235,10 +1230,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>569020</v>
+        <v>568969</v>
       </c>
       <c r="R7" t="n">
-        <v>7107958</v>
+        <v>7107966</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1297,10 +1292,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122131801</v>
+        <v>122132185</v>
       </c>
       <c r="B8" t="n">
-        <v>90826</v>
+        <v>57399</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1313,21 +1308,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1337,10 +1332,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>569094</v>
+        <v>568955</v>
       </c>
       <c r="R8" t="n">
-        <v>7107950</v>
+        <v>7108055</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1399,10 +1394,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122131771</v>
+        <v>122131750</v>
       </c>
       <c r="B9" t="n">
-        <v>79765</v>
+        <v>78656</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1411,25 +1406,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1439,10 +1434,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>569099</v>
+        <v>568985</v>
       </c>
       <c r="R9" t="n">
-        <v>7107950</v>
+        <v>7107948</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1501,10 +1496,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122131750</v>
+        <v>122132182</v>
       </c>
       <c r="B10" t="n">
-        <v>78656</v>
+        <v>57383</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1517,21 +1512,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1541,10 +1536,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>568985</v>
+        <v>568987</v>
       </c>
       <c r="R10" t="n">
-        <v>7107948</v>
+        <v>7107945</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1577,6 +1572,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-10-08</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>hackspår äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
